--- a/Assets/Excel/NPC配置表.xlsx
+++ b/Assets/Excel/NPC配置表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\TurnDemo\Assets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>f_id</t>
   </si>
@@ -47,6 +52,12 @@
     <t>f_dialogueId</t>
   </si>
   <si>
+    <t>f_controllerAssetKey</t>
+  </si>
+  <si>
+    <t>f_animProfile</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -74,6 +85,12 @@
     <t>对话起始ID</t>
   </si>
   <si>
+    <t>控制器资源key</t>
+  </si>
+  <si>
+    <t>使用的动画配置文件</t>
+  </si>
+  <si>
     <t>史蒂夫</t>
   </si>
   <si>
@@ -84,6 +101,12 @@
   </si>
   <si>
     <t>村民</t>
+  </si>
+  <si>
+    <t>NpcController</t>
+  </si>
+  <si>
+    <t>NpcAnimationConfig</t>
   </si>
   <si>
     <t>流浪者</t>
@@ -1026,8 +1049,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.8916666666667" customWidth="1"/>
     <col min="2" max="2" width="33.6666666666667" customWidth="1"/>
@@ -1035,9 +1058,11 @@
     <col min="4" max="4" width="39.4416666666667" customWidth="1"/>
     <col min="5" max="5" width="19.225" customWidth="1"/>
     <col min="6" max="6" width="27.5583333333333" customWidth="1"/>
+    <col min="7" max="7" width="23.8" customWidth="1"/>
+    <col min="8" max="8" width="25.325" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1056,90 +1081,120 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:6">
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
